--- a/report_templates/Delivery Status.xlsx
+++ b/report_templates/Delivery Status.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\git hub repositeries\GRP_SYS\report_templates\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4651BEF0-060A-4C26-85A0-690860AA7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{4651BEF0-060A-4C26-85A0-690860AA7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A96F8DBF-C8FE-4F0D-ACD8-FF970016EBF6}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,20 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
-  <si>
-    <t xml:space="preserve">           CUSTOMER</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve">   CONTACT PERSON</t>
   </si>
   <si>
-    <t xml:space="preserve">   PHONE NUMBER</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                                 REMARKS</t>
-  </si>
-  <si>
     <t xml:space="preserve">   LOCATION</t>
   </si>
   <si>
@@ -65,9 +56,6 @@
     <t xml:space="preserve">   DEL. DATE</t>
   </si>
   <si>
-    <t>DEL.STATUS</t>
-  </si>
-  <si>
     <t>DEL. COMP. DATE</t>
   </si>
   <si>
@@ -75,13 +63,28 @@
   </si>
   <si>
     <t xml:space="preserve"> TYPE</t>
+  </si>
+  <si>
+    <t>CUSTOMER</t>
+  </si>
+  <si>
+    <t>REMARKS</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> PHONE NUMBER</t>
+  </si>
+  <si>
+    <t>DELIVERY STATUS</t>
+  </si>
+  <si>
+    <t>Qty</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -104,6 +107,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -119,12 +130,27 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -133,10 +159,12 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -152,6 +180,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -417,85 +449,89 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.1796875" customWidth="1"/>
     <col min="2" max="2" width="22.26953125" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="8.1796875" customWidth="1"/>
-    <col min="5" max="5" width="5.81640625" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
-    <col min="7" max="7" width="11.26953125" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" customWidth="1"/>
-    <col min="9" max="9" width="16" customWidth="1"/>
-    <col min="10" max="10" width="20.1796875" customWidth="1"/>
-    <col min="11" max="12" width="16.1796875" customWidth="1"/>
-    <col min="13" max="13" width="95.26953125" customWidth="1"/>
+    <col min="3" max="3" width="22.08984375" customWidth="1"/>
+    <col min="4" max="4" width="12.08984375" customWidth="1"/>
+    <col min="5" max="5" width="12.1796875" customWidth="1"/>
+    <col min="6" max="6" width="8.1796875" customWidth="1"/>
+    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="8" max="8" width="11.26953125" customWidth="1"/>
+    <col min="9" max="9" width="36.54296875" customWidth="1"/>
+    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="11" max="11" width="20.1796875" customWidth="1"/>
+    <col min="12" max="13" width="16.1796875" customWidth="1"/>
+    <col min="14" max="14" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="I1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="L1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="N1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="2"/>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="2"/>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="2"/>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="M8" s="4"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="1"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="1"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="1"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="1"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="N7" s="2"/>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/report_templates/Delivery Status.xlsx
+++ b/report_templates/Delivery Status.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/3b68409331e52ac1/Documents/GRP/GRP_SYS/report_templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{4651BEF0-060A-4C26-85A0-690860AA7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A96F8DBF-C8FE-4F0D-ACD8-FF970016EBF6}"/>
+  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{4651BEF0-060A-4C26-85A0-690860AA7B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{865F73C5-CD7E-45CA-8EBA-E087624F1558}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t xml:space="preserve">   CONTACT PERSON</t>
   </si>
@@ -47,18 +47,12 @@
     <t>W.O.NO.</t>
   </si>
   <si>
-    <t>TANK SIZE</t>
-  </si>
-  <si>
     <t xml:space="preserve"> BRAND</t>
   </si>
   <si>
     <t xml:space="preserve">   DEL. DATE</t>
   </si>
   <si>
-    <t>DEL. COMP. DATE</t>
-  </si>
-  <si>
     <t>SALES PERSON</t>
   </si>
   <si>
@@ -78,6 +72,9 @@
   </si>
   <si>
     <t>Qty</t>
+  </si>
+  <si>
+    <t>TANK SIZE/MATERIAL</t>
   </si>
 </sst>
 </file>
@@ -449,89 +446,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N8"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.1796875" customWidth="1"/>
     <col min="2" max="2" width="22.26953125" customWidth="1"/>
-    <col min="3" max="3" width="22.08984375" customWidth="1"/>
-    <col min="4" max="4" width="12.08984375" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" customWidth="1"/>
-    <col min="6" max="6" width="8.1796875" customWidth="1"/>
-    <col min="7" max="7" width="11" customWidth="1"/>
+    <col min="3" max="3" width="12.1796875" customWidth="1"/>
+    <col min="4" max="4" width="11" customWidth="1"/>
+    <col min="5" max="5" width="25.54296875" customWidth="1"/>
+    <col min="6" max="6" width="12.08984375" customWidth="1"/>
+    <col min="7" max="7" width="8.1796875" customWidth="1"/>
     <col min="8" max="8" width="11.26953125" customWidth="1"/>
     <col min="9" max="9" width="36.54296875" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="20.1796875" customWidth="1"/>
-    <col min="12" max="13" width="16.1796875" customWidth="1"/>
-    <col min="14" max="14" width="61.81640625" customWidth="1"/>
+    <col min="10" max="10" width="20.1796875" customWidth="1"/>
+    <col min="11" max="12" width="16.1796875" customWidth="1"/>
+    <col min="13" max="13" width="61.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" s="4" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="E1" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="I1" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1"/>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1"/>
       <c r="H7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="N7" s="2"/>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="N8" s="3"/>
+      <c r="K7" s="1"/>
+      <c r="M7" s="2"/>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="M8" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
